--- a/packages/importers/src/xtb/fixture/xtb-sample.xlsx
+++ b/packages/importers/src/xtb/fixture/xtb-sample.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="119">
   <si>
     <t>Account number</t>
   </si>
@@ -339,6 +339,18 @@
     <t>Volume</t>
   </si>
   <si>
+    <t>Spinoff Co</t>
+  </si>
+  <si>
+    <t>SPIN.PL</t>
+  </si>
+  <si>
+    <t>1000000009</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+  <si>
     <t>Closed Positions</t>
   </si>
   <si>
@@ -352,9 +364,6 @@
   </si>
   <si>
     <t>Close Time (UTC)</t>
-  </si>
-  <si>
-    <t>BUY</t>
   </si>
   <si>
     <t>Profit/loss</t>
@@ -1589,7 +1598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1730,6 +1739,52 @@
       </c>
       <c r="F14">
         <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>0.01</v>
+      </c>
+      <c r="J16" s="1">
+        <v>45519.33333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1808,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1792,16 +1847,16 @@
         <v>107</v>
       </c>
       <c r="F5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1815,7 +1870,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1835,10 +1890,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
